--- a/warehouse/warehouse.xlsx
+++ b/warehouse/warehouse.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D454"/>
+  <dimension ref="A1:D534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17155,6 +17155,1766 @@
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Row 1 (Monday)</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>Row 2 (Monday)</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>SUNRISE DIGEST</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Row 6 (Monday)</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>WAKE UP UGANDA</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>Row 10 (Monday)</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>BREAKFAST BITES</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Row 12 (Monday)</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>BRIGHTWAVE SQ BK</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>Row 13 (Monday)</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>AM DRIVE</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Row 15 (Monday)</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>CITY PULSE</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>Row 18 (Monday)</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Row 21 (Monday)</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>EMERALDTEL SQ BK</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>Row 22 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>ZENGLOW TVC</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Row 24 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>SUNRISE DIGEST</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>Row 25 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Row 29 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>ZAWADI FASHION SQ BK</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ZAWADI FASHION SQZBK' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>Row 30 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>WAKE UP UGANDA</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Row 31 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>Row 32 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Row 33 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>BREAKFAST BITES</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>Row 36 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>AM DRIVE</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Row 37 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>NYATI MOTORS PROMO</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>Row 38 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>CITY PULSE</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Row 42 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>Row 46 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>BRIGHTWAVE SQ BK</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Row 47 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>SUNRISE DIGEST</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>Row 51 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>BRIGHTWAVE SQ BK</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Row 52 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>WAKE UP UGANDA</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>Row 53 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>TERALINK SQ BK</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Row 54 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>BRIGHTWAVE SQ BK</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>Row 55 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>BREAKFAST BITES</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D482" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Row 58 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>Row 60 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D484" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Row 61 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>AM DRIVE</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>Row 62 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>TERALINK SQ BK</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D486" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Row 63 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>Row 64 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>TWIGA AIRTIME TVC</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'TWIGA AIRTIME' (95.0%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D488" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Row 65 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>CITY PULSE</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>Row 66 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>ZENGLOW TVC</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D490" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Row 67 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>Row 68 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>SUNRISE DIGEST</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D492" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Row 69 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>Row 70 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>WAKE UP UGANDA</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D494" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Row 72 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>BREAKFAST BITES</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>Row 74 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>ZENGLOW TVC</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D496" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Row 75 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>Row 76 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D498" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Row 78 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>Row 80 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>AM DRIVE</t>
+        </is>
+      </c>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D500" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Row 82 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>EMERALDTEL SQ BK</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>Row 83 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <t>CITY PULSE</t>
+        </is>
+      </c>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D502" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Row 84 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>Row 86 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>HIGHLAND BREW TVC</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D504" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Row 88 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>PEMBA TYRES PROMO</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>Row 91 (Friday)</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Row 92 (Friday)</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>Row 93 (Friday)</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Row 94 (Friday)</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>Row 95 (Friday)</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>SUNRISE DIGEST</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D510" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Row 97 (Friday)</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>Row 98 (Friday)</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <t>WAKE UP UGANDA</t>
+        </is>
+      </c>
+      <c r="C512" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D512" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Row 99 (Friday)</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>PEMBA TYRES PROMO</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>Row 100 (Friday)</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>BRIGHTWAVE SQ BK</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Row 101 (Friday)</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>BREAKFAST BITES</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>Row 102 (Friday)</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D516" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Row 103 (Friday)</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>Row 104 (Friday)</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>HIGHLAND BREW TVC</t>
+        </is>
+      </c>
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Row 105 (Friday)</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>NYATI MOTORS PROMO</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>Row 106 (Friday)</t>
+        </is>
+      </c>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C520" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D520" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Row 107 (Friday)</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>Row 108 (Friday)</t>
+        </is>
+      </c>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <t>AM DRIVE</t>
+        </is>
+      </c>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D522" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Row 110 (Friday)</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>CITY PULSE</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>Row 113 (Friday)</t>
+        </is>
+      </c>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <t>TERALINK SQ BK</t>
+        </is>
+      </c>
+      <c r="C524" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D524" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Row 115 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>SUNRISE DIGEST</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>Row 117 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>WAKE UP UGANDA</t>
+        </is>
+      </c>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D526" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Row 118 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>EMERALDTEL SQ BK</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>Row 120 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>HIGHLAND BREW TVC</t>
+        </is>
+      </c>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D528" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Row 121 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>Row 122 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C530" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D530" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Row 126 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>NYATI MOTORS PROMO</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>Row 129 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>EMERALDTEL SQ BK</t>
+        </is>
+      </c>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D532" s="2" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Row 130 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>BREAKFAST BITES</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>No category match found</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Assign category in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>Row 131 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D534" s="2" t="inlineStr">
         <is>
           <t>Confirm match is correct in Mapping Manager</t>
         </is>
@@ -18046,7 +19806,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>453</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8">
@@ -18067,7 +19827,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30.07.2026 16:03</t>
+          <t>30.07.2026 16:04</t>
         </is>
       </c>
     </row>

--- a/warehouse/warehouse.xlsx
+++ b/warehouse/warehouse.xlsx
@@ -12,7 +12,6 @@
     <sheet name="Flags Log" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Dropped Rows Log" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Day Detection Log" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -641,7 +640,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -841,7 +840,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1041,7 +1040,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1141,7 +1140,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1191,7 +1190,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1291,7 +1290,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1591,7 +1590,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1641,7 +1640,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1741,7 +1740,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2041,7 +2040,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2191,7 +2190,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2341,7 +2340,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2391,7 +2390,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2441,7 +2440,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2841,7 +2840,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2891,7 +2890,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3091,7 +3090,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3141,7 +3140,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3191,7 +3190,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3241,7 +3240,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3291,7 +3290,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3591,7 +3590,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3641,7 +3640,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3791,7 +3790,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3841,7 +3840,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3941,7 +3940,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -4041,7 +4040,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -4141,7 +4140,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -4241,7 +4240,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -4541,7 +4540,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4641,7 +4640,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4691,7 +4690,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4841,7 +4840,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -4941,7 +4940,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -5291,7 +5290,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5441,7 +5440,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -5491,7 +5490,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5541,7 +5540,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5591,7 +5590,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5741,7 +5740,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -5791,7 +5790,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5941,7 +5940,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -6041,7 +6040,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -6191,7 +6190,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6291,7 +6290,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -6391,7 +6390,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6441,7 +6440,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -6541,7 +6540,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -6841,7 +6840,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -6991,7 +6990,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7041,7 +7040,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>****</t>
+          <t>Franchise</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -7106,11 +7105,6 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="H2:H133" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Commercial,Internal,Trade Marketing,Swap,Franchise"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19722,116 +19716,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Total Rows in Warehouse</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Total Weeks Stored</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Total ADs</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Total SQs</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Total Corrections</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Total Flags</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Total Dropped Rows</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Last Updated</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>30.07.2026 16:04</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/warehouse/warehouse.xlsx
+++ b/warehouse/warehouse.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Flags Log" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Dropped Rows Log" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Day Detection Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -550,7 +551,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -600,7 +601,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -650,7 +651,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -700,7 +701,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -750,7 +751,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -800,7 +801,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -850,7 +851,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -900,7 +901,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -950,7 +951,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1001,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1051,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1101,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1151,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1201,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1251,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1301,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1351,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1401,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1451,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1501,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1551,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1601,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1651,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1701,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1751,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1801,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1851,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1901,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1951,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2001,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2051,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2101,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2151,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2201,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2251,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2301,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2351,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2401,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2451,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2501,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2551,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2601,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2651,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2701,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2751,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2801,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2851,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2901,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2951,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3001,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3051,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3101,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3151,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3201,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3251,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3301,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3351,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3401,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3451,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3501,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3550,7 +3551,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3601,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3651,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3701,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3751,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3801,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3851,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3901,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3951,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4001,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4051,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4101,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4151,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4201,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4251,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4301,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4351,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4401,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4451,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4501,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4551,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4601,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4651,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4701,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4751,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4801,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4851,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4901,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -4950,7 +4951,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5001,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5051,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5101,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5151,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5201,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5251,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5300,7 +5301,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5351,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5401,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5451,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5501,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5551,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5600,7 +5601,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5650,7 +5651,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5701,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5751,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5801,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5851,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5901,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -5950,7 +5951,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6001,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6051,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6101,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6151,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6201,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6251,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6301,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6351,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6401,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6451,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6501,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6551,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6601,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6651,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6701,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6751,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6801,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6851,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6900,7 +6901,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6951,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -7000,7 +7001,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7051,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
@@ -7100,11 +7101,1116 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>30.07.2026 16:04</t>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>BLUERIVER PAINTS PROMO</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>06:07am</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>06:12am</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>30</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>SUNRISE DIGEST</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>06:12am</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Franchise</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>FALCON EXPRESS LOGISTICS PROMO</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>06:13am</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>30</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Swap</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>LUMO ELECTRONICS PROMO</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>06:18am</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Swap</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NILE CREST WATER SQ BK</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>06:23am</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>30</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>WAKE UP UGANDA</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>06:23am</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Franchise</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>MAMA'S CHOICE FOODS PROMO</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>06:26am</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>30</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Trade Marketing</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>GOLDTUSK BANK PROMO</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>06:30am</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Franchise</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>KATO'S HARDWARE TVC</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>06:33am</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>30</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>BREAKFAST BITES</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>06:33am</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Franchise</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>CRESTA FUELS SQ BK</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>06:34am</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>30</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Swap</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>BRIGHTWAVE SQ BK</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>06:35am</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Franchise</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>AM DRIVE</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>06:35am</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>40</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Franchise</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>KATO'S HARDWARE TVC</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>06:41am</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>CITY PULSE</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>06:41am</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>40</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Franchise</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>GOLDTUSK BANK PROMO</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>06:49am</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Franchise</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NILE CREST WATER SQ BK</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>06:50am</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>30</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>06:56am</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Trade Marketing</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>KAMPALA FRESH DAIRY SQ BK</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>06:58am</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>30</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Trade Marketing</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>KAMPALA FRESH DAIRY SQ BK</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>06:59am</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>6am</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Trade Marketing</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>EMERALDTEL SQ BK</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>07:00am</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>7am</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>30</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Franchise</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="H2:H155" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Commercial,Internal,Trade Marketing,Swap,Franchise"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7157,7 +8263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D534"/>
+  <dimension ref="A1:D565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18909,6 +20015,688 @@
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Row 1 (Monday)</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>Row 18 (Monday)</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D536" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Row 25 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>Row 29 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>ZAWADI FASHION SQ BK</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ZAWADI FASHION SQZBK' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D538" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Row 31 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>Row 32 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D540" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Row 42 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>Row 58 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D542" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Row 60 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>Row 63 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Row 64 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>TWIGA AIRTIME TVC</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'TWIGA AIRTIME' (95.0%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>Row 67 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D546" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Row 69 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>Row 75 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Row 76 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>Row 78 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Row 84 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>Row 91 (Friday)</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Row 92 (Friday)</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>Row 93 (Friday)</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Row 94 (Friday)</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>Row 97 (Friday)</t>
+        </is>
+      </c>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Row 102 (Friday)</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>Row 103 (Friday)</t>
+        </is>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D558" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Row 106 (Friday)</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>Row 107 (Friday)</t>
+        </is>
+      </c>
+      <c r="B560" s="2" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C560" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D560" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Row 121 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="inlineStr">
+        <is>
+          <t>Row 122 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C562" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D562" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Row 131 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>Row 133 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Row 150 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
         <is>
           <t>Confirm match is correct in Mapping Manager</t>
         </is>
@@ -18925,7 +20713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -19455,6 +21243,117 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Row 3 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MORNING BREEZE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Excluded - operational or schedule text, not an ad</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Row 9 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>PURENECTAR PROMO</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>SQ</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Marked not aired</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Row 23 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MORNING BREEZE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Excluded - operational or schedule text, not an ad</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19466,7 +21365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19713,6 +21612,151 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2026</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>08.06.2026 to 14.06.2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Total Rows in Warehouse</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Total Weeks Stored</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Total ADs</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total SQs</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Total Corrections</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total Flags</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Total Dropped Rows</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30.07.2026 20:58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/warehouse/warehouse.xlsx
+++ b/warehouse/warehouse.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8971,6 +8971,688 @@
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Row 1 (Monday)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Row 18 (Monday)</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Row 25 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Row 29 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>ZAWADI FASHION SQ BK</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ZAWADI FASHION SQZBK' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Row 31 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Row 32 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Row 42 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Row 58 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Row 60 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Row 63 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Row 64 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TWIGA AIRTIME TVC</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'TWIGA AIRTIME' (95.0%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Row 67 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Row 69 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Row 75 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Row 76 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Row 78 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Row 84 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Row 91 (Friday)</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Row 92 (Friday)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Row 93 (Friday)</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Row 94 (Friday)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Row 97 (Friday)</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Row 102 (Friday)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Row 103 (Friday)</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Row 106 (Friday)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Row 107 (Friday)</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Row 121 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Row 122 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Row 131 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Row 133 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Row 150 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>Confirm match is correct in Mapping Manager</t>
         </is>
@@ -10006,7 +10688,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -10027,7 +10709,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30.07.2026 21:11</t>
+          <t>30.07.2026 21:14</t>
         </is>
       </c>
     </row>

--- a/warehouse/warehouse.xlsx
+++ b/warehouse/warehouse.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9653,6 +9653,688 @@
         </is>
       </c>
       <c r="D63" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Row 1 (Monday)</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Row 18 (Monday)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Row 25 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Row 29 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ZAWADI FASHION SQ BK</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ZAWADI FASHION SQZBK' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Row 31 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Row 32 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Row 42 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Row 58 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Row 60 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Row 63 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Row 64 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>TWIGA AIRTIME TVC</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'TWIGA AIRTIME' (95.0%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Row 67 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Row 69 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Row 75 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Row 76 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Row 78 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Row 84 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Row 91 (Friday)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Row 92 (Friday)</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Row 93 (Friday)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Row 94 (Friday)</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Row 97 (Friday)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Row 102 (Friday)</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Row 103 (Friday)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Row 106 (Friday)</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Row 107 (Friday)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Row 121 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Row 122 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Row 131 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Row 133 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Row 150 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Confirm match is correct in Mapping Manager</t>
         </is>
@@ -10688,7 +11370,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8">
@@ -10709,7 +11391,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30.07.2026 21:14</t>
+          <t>30.07.2026 21:52</t>
         </is>
       </c>
     </row>

--- a/warehouse/warehouse.xlsx
+++ b/warehouse/warehouse.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10335,6 +10335,688 @@
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Row 1 (Monday)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Row 18 (Monday)</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Row 25 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Row 29 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>ZAWADI FASHION SQ BK</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ZAWADI FASHION SQZBK' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Row 31 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Row 32 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Row 42 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Row 58 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Row 60 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Row 63 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Row 64 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>TWIGA AIRTIME TVC</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'TWIGA AIRTIME' (95.0%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Row 67 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Row 69 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Row 75 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Row 76 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Row 78 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Row 84 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Row 91 (Friday)</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Row 92 (Friday)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Row 93 (Friday)</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Row 94 (Friday)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Row 97 (Friday)</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Row 102 (Friday)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Row 103 (Friday)</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Row 106 (Friday)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Row 107 (Friday)</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Row 121 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Row 122 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Row 131 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Row 133 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Row 150 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
         <is>
           <t>Confirm match is correct in Mapping Manager</t>
         </is>
@@ -11370,7 +12052,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8">
@@ -11391,7 +12073,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30.07.2026 21:52</t>
+          <t>30.07.2026 22:03</t>
         </is>
       </c>
     </row>

--- a/warehouse/warehouse.xlsx
+++ b/warehouse/warehouse.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11017,6 +11017,688 @@
         </is>
       </c>
       <c r="D125" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Row 1 (Monday)</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Row 18 (Monday)</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Row 25 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Row 29 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>ZAWADI FASHION SQ BK</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ZAWADI FASHION SQZBK' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Row 31 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Row 32 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Row 42 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Row 58 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Row 60 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Row 63 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Row 64 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>TWIGA AIRTIME TVC</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'TWIGA AIRTIME' (95.0%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Row 67 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Row 69 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Row 75 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Row 76 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Row 78 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Row 84 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Row 91 (Friday)</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Row 92 (Friday)</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Row 93 (Friday)</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Row 94 (Friday)</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Row 97 (Friday)</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Row 102 (Friday)</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Row 103 (Friday)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Row 106 (Friday)</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Row 107 (Friday)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Row 121 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Row 122 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Row 131 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Row 133 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Row 150 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Confirm match is correct in Mapping Manager</t>
         </is>
@@ -12052,7 +12734,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>124</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8">
@@ -12073,7 +12755,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30.07.2026 22:03</t>
+          <t>30.07.2026 22:12</t>
         </is>
       </c>
     </row>

--- a/warehouse/warehouse.xlsx
+++ b/warehouse/warehouse.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D156"/>
+  <dimension ref="A1:D187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11699,6 +11699,688 @@
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Row 1 (Monday)</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Row 18 (Monday)</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Row 25 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Row 29 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>ZAWADI FASHION SQ BK</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ZAWADI FASHION SQZBK' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Row 31 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Row 32 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Row 42 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Row 58 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Row 60 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Row 63 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Row 64 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>TWIGA AIRTIME TVC</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'TWIGA AIRTIME' (95.0%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Row 67 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Row 69 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Row 75 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Row 76 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Row 78 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Row 84 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Row 91 (Friday)</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Row 92 (Friday)</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Row 93 (Friday)</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Row 94 (Friday)</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Row 97 (Friday)</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Row 102 (Friday)</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Row 103 (Friday)</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Row 106 (Friday)</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Row 107 (Friday)</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Row 121 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Row 122 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Row 131 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Row 133 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Row 150 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
         <is>
           <t>Confirm match is correct in Mapping Manager</t>
         </is>
@@ -12734,7 +13416,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>155</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8">
@@ -12755,7 +13437,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30.07.2026 22:12</t>
+          <t>30.07.2026 22:15</t>
         </is>
       </c>
     </row>

--- a/warehouse/warehouse.xlsx
+++ b/warehouse/warehouse.xlsx
@@ -8263,7 +8263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D187"/>
+  <dimension ref="A1:D218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12381,6 +12381,688 @@
         </is>
       </c>
       <c r="D187" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Row 1 (Monday)</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Row 18 (Monday)</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Row 25 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Row 29 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ZAWADI FASHION SQ BK</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ZAWADI FASHION SQZBK' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Row 31 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Row 32 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Row 42 (Tuesday)</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Row 58 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Row 60 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Row 63 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Row 64 (Wednesday)</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>TWIGA AIRTIME TVC</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'TWIGA AIRTIME' (95.0%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Row 67 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Row 69 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Row 75 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Row 76 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Row 78 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Row 84 (Thursday)</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Row 91 (Friday)</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Row 92 (Friday)</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Row 93 (Friday)</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Row 94 (Friday)</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Row 97 (Friday)</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Row 102 (Friday)</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Row 103 (Friday)</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Row 106 (Friday)</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>RIDGEWAY FURNITURE TVC</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'RIDGEWAY FURNITURE' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Row 107 (Friday)</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>ROLEX EXPRESS TVC</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'ROLEX EXPRESS' (95.0%) - assigned Swap</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Row 121 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>CEDAR GROVE REALTY SQ BK</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CEDAR GROVE REALTY SQZBK' (95.8%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Row 122 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Row 131 (Saturday)</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>CRESTLINE FOODS SQ BK</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'CRESTLINE FOODS SQZBK' (95.2%) - assigned Commercial</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Row 133 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>NALU COSMETICS SQ BK</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'NALU COSMETICS SQZBK' (95.0%) - assigned Internal</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Confirm match is correct in Mapping Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Row 150 (Sunday)</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>AMARA SKINCARE TVC</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy matched to 'AMARA SKINCARE' (95.0%) - assigned Trade Marketing</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>Confirm match is correct in Mapping Manager</t>
         </is>
@@ -13416,7 +14098,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>186</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8">
